--- a/data/trans_orig/P33B_R1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R1-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>59057</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>75692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60401</t>
+          <t>66754</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72203</t>
+          <t>80565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>115853</t>
+          <t>125811</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98909</t>
+          <t>106830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>147469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>449760</t>
+          <t>491561</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435927</t>
+          <t>474926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462464</t>
+          <t>505058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>387066</t>
+          <t>421657</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375264</t>
+          <t>407846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397262</t>
+          <t>433691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>836826</t>
+          <t>913218</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>816896</t>
+          <t>891560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>853770</t>
+          <t>932199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>53420</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>68824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66728</t>
+          <t>74939</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>89630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>117480</t>
+          <t>128359</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101074</t>
+          <t>110356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137567</t>
+          <t>150042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>401461</t>
+          <t>429792</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386798</t>
+          <t>414388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414121</t>
+          <t>442383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>315852</t>
+          <t>348204</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302531</t>
+          <t>333513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328692</t>
+          <t>361249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>717313</t>
+          <t>777996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697226</t>
+          <t>756313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733719</t>
+          <t>795999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>78888</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>62708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125606</t>
+          <t>94774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>49966</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35486</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55062</t>
+          <t>62419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>119113</t>
+          <t>128854</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>108816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174637</t>
+          <t>147524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>593662</t>
+          <t>392724</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542658</t>
+          <t>376838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639474</t>
+          <t>408904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>121834</t>
+          <t>136963</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130859</t>
+          <t>147434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>715496</t>
+          <t>529686</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659972</t>
+          <t>511016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>782899</t>
+          <t>549724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>134738</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114973</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155419</t>
+          <t>170696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>140719</t>
+          <t>160302</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80967</t>
+          <t>139568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185081</t>
+          <t>178799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275456</t>
+          <t>308232</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180255</t>
+          <t>280907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314818</t>
+          <t>337135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>900081</t>
+          <t>983913</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>879400</t>
+          <t>961147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919846</t>
+          <t>1005495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>837375</t>
+          <t>700909</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>793013</t>
+          <t>682412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>897127</t>
+          <t>721643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1737456</t>
+          <t>1684822</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1698094</t>
+          <t>1655919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1832657</t>
+          <t>1712147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>75721</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54959</t>
+          <t>60442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84627</t>
+          <t>92370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>199052</t>
+          <t>222868</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148290</t>
+          <t>202306</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>230279</t>
+          <t>244183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>267095</t>
+          <t>298589</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213426</t>
+          <t>272565</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298206</t>
+          <t>324589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>405972</t>
+          <t>491161</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389389</t>
+          <t>474512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419057</t>
+          <t>506440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>639944</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608717</t>
+          <t>585944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>690706</t>
+          <t>627821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1045917</t>
+          <t>1098420</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1014806</t>
+          <t>1072420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099586</t>
+          <t>1124444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22920</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>41028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>183867</t>
+          <t>204617</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165154</t>
+          <t>181026</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205700</t>
+          <t>229407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>206787</t>
+          <t>227231</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182335</t>
+          <t>202326</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233667</t>
+          <t>255118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>217587</t>
+          <t>214614</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200682</t>
+          <t>196200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228537</t>
+          <t>224529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>577504</t>
+          <t>639664</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>555671</t>
+          <t>614874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596217</t>
+          <t>663255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>795091</t>
+          <t>854278</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>768211</t>
+          <t>826391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>819543</t>
+          <t>879183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>406507</t>
+          <t>437630</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>322255</t>
+          <t>399040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>455755</t>
+          <t>477770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>695278</t>
+          <t>779446</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>571235</t>
+          <t>740318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>758369</t>
+          <t>822938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1101785</t>
+          <t>1217075</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>942756</t>
+          <t>1157090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1192321</t>
+          <t>1275861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2968524</t>
+          <t>3003764</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2919276</t>
+          <t>2963624</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3052776</t>
+          <t>3042354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2879575</t>
+          <t>2854656</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2816484</t>
+          <t>2811164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3003618</t>
+          <t>2893784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5848099</t>
+          <t>5858421</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5757563</t>
+          <t>5799635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6007128</t>
+          <t>5918406</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574853</t>
+          <t>3634102</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574853</t>
+          <t>3634102</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574853</t>
+          <t>3634102</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6949884</t>
+          <t>7075496</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6949884</t>
+          <t>7075496</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6949884</t>
+          <t>7075496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
